--- a/backend/data/uploads/MES/2026-07-15_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-15_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F65BC706-651A-49F1-92FF-3FB341326C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{340A9330-39DC-40A4-BEBB-C809ABF2336C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{2F365524-FB09-436A-9C0C-1C931B4B9ED8}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{4DC4040B-522B-4108-9C01-4A894F8266C5}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7F1211-08E5-4C0B-B40B-379B346C7E95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071A7D28-B573-4591-BB41-CBD40033DD95}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-15_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-15_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{340A9330-39DC-40A4-BEBB-C809ABF2336C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EF7351D-2DD6-45A0-B9DB-65EA02C4013F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{4DC4040B-522B-4108-9C01-4A894F8266C5}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{942EAEBA-088A-4C77-9F6C-F8479ED38D8B}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{071A7D28-B573-4591-BB41-CBD40033DD95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975E893D-B33B-4949-BFD0-5FE388E95104}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-15_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-15_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7EF7351D-2DD6-45A0-B9DB-65EA02C4013F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6688A0F3-0824-400A-90C5-38BD21A0235B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{942EAEBA-088A-4C77-9F6C-F8479ED38D8B}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{A8CBC136-4BAF-47EE-8A73-9711B0360AE9}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{975E893D-B33B-4949-BFD0-5FE388E95104}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19C6E7C9-0879-46F9-8ABD-5CCC297D2701}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
